--- a/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 7,78</t>
+          <t>-0,84; 7,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 9,25</t>
+          <t>0,08; 9,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -1,57</t>
+          <t>-7,17; -1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,74</t>
+          <t>0,61; 8,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 9,27</t>
+          <t>0,94; 9,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,72</t>
+          <t>-2,5; 6,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,84</t>
+          <t>1,04; 7,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,04</t>
+          <t>2,23; 7,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,33</t>
+          <t>-3,85; 1,41</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 348,59</t>
+          <t>-19,43; 310,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 425,58</t>
+          <t>-10,09; 407,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-98,28; -74,74</t>
+          <t>-98,44; -78,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 642,04</t>
+          <t>-2,83; 681,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 646,38</t>
+          <t>2,36; 673,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,93; 499,13</t>
+          <t>-68,69; 561,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 302,91</t>
+          <t>16,92; 319,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,03; 347,78</t>
+          <t>41,28; 385,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 88,56</t>
+          <t>-81,01; 117,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,76</t>
+          <t>-1,67; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,44</t>
+          <t>-2,02; 4,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 3,46</t>
+          <t>-3,84; 3,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,67</t>
+          <t>-5,74; 0,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,57</t>
+          <t>-4,71; 2,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -2,47</t>
+          <t>-7,92; -2,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,41</t>
+          <t>-2,88; 1,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,33</t>
+          <t>-2,14; 2,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -0,44</t>
+          <t>-5,0; -0,45</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 109,37</t>
+          <t>-26,29; 105,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 102,34</t>
+          <t>-27,04; 100,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 78,14</t>
+          <t>-56,56; 83,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 12,76</t>
+          <t>-57,26; 10,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 24,52</t>
+          <t>-47,98; 33,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,89; -32,81</t>
+          <t>-78,95; -33,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,21; 25,96</t>
+          <t>-35,81; 29,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 39,23</t>
+          <t>-27,75; 42,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,5; -4,67</t>
+          <t>-62,76; -3,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -0,47</t>
+          <t>-8,0; -0,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,59; -2,51</t>
+          <t>-10,24; -2,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 1,08</t>
+          <t>-7,14; 0,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 1,24</t>
+          <t>-5,89; 1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,68</t>
+          <t>-6,1; 0,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,65</t>
+          <t>-6,58; 0,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; -0,56</t>
+          <t>-5,67; -0,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; -1,72</t>
+          <t>-6,75; -1,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; -0,38</t>
+          <t>-5,53; -0,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,29; -2,68</t>
+          <t>-76,9; -6,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,22; -35,75</t>
+          <t>-93,57; -40,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,03; 34,15</t>
+          <t>-72,46; 21,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 31,84</t>
+          <t>-68,6; 35,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 20,64</t>
+          <t>-67,12; 24,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,68; 17,38</t>
+          <t>-73,8; 10,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,07; -8,95</t>
+          <t>-66,22; -9,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,92; -25,94</t>
+          <t>-76,29; -30,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,43; -3,12</t>
+          <t>-62,54; -3,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,51</t>
+          <t>-0,78; 4,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,43</t>
+          <t>2,54; 9,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,88</t>
+          <t>-4,67; -0,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,2</t>
+          <t>-2,96; 2,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,8</t>
+          <t>-0,89; 4,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -1,01</t>
+          <t>-5,17; -0,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,42</t>
+          <t>-1,0; 2,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,05</t>
+          <t>1,52; 6,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,97; -1,37</t>
+          <t>-4,06; -1,23</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 439,57</t>
+          <t>-31,29; 378,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,86; 850,04</t>
+          <t>45,52; 788,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 98,09</t>
+          <t>-58,48; 110,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 196,79</t>
+          <t>-26,02; 210,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-95,39; -28,03</t>
+          <t>-95,04; -24,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 116,16</t>
+          <t>-27,04; 144,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,15; 277,15</t>
+          <t>28,78; 268,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-95,3; -51,15</t>
+          <t>-95,13; -52,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 4,43</t>
+          <t>-3,54; 4,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,68</t>
+          <t>-4,26; 2,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -1,28</t>
+          <t>-7,47; -1,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,14</t>
+          <t>-3,87; 5,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 1,66</t>
+          <t>-6,29; 1,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -1,48</t>
+          <t>-8,37; -1,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,78</t>
+          <t>-2,38; 3,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,24</t>
+          <t>-4,11; 0,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -1,77</t>
+          <t>-6,25; -1,83</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-67,14; 296,33</t>
+          <t>-70,78; 278,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-76,54; 237,24</t>
+          <t>-78,12; 194,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 161,73</t>
+          <t>-53,35; 163,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,53; 60,73</t>
+          <t>-77,39; 62,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-97,62; -1,39</t>
+          <t>-97,35; -13,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 133,46</t>
+          <t>-40,65; 136,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-71,37; 51,03</t>
+          <t>-68,83; 38,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-97,33; -37,84</t>
+          <t>-97,72; -31,9</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,31</t>
+          <t>-2,51; 2,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,24</t>
+          <t>-2,79; 1,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,42</t>
+          <t>-2,28; 2,27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,78</t>
+          <t>-2,52; 3,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,47</t>
+          <t>-5,36; -0,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,23</t>
+          <t>-4,04; 1,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,47</t>
+          <t>-1,56; 2,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,17</t>
+          <t>-3,18; -0,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,41</t>
+          <t>-2,24; 1,26</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 370,77</t>
+          <t>-87,3; 374,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 249,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-76,1; 402,94</t>
+          <t>-74,6; 355,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-55,57; 208,0</t>
+          <t>-54,13; 215,72</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,41</t>
+          <t>-100,0; 31,55</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-81,28; 81,49</t>
+          <t>-80,51; 101,27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-46,51; 178,62</t>
+          <t>-46,19; 140,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-90,44; 16,23</t>
+          <t>-90,3; 4,54</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-62,65; 96,55</t>
+          <t>-63,94; 85,74</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,83</t>
+          <t>-2,93; 2,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,23</t>
+          <t>-4,4; 0,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,15</t>
+          <t>-3,63; 1,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,98</t>
+          <t>-2,21; 3,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,65; -1,8</t>
+          <t>-7,58; -1,88</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -2,28</t>
+          <t>-8,89; -2,24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,27</t>
+          <t>-2,04; 2,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -1,71</t>
+          <t>-5,15; -1,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,25; -1,27</t>
+          <t>-5,28; -1,25</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 50,21</t>
+          <t>-45,85; 58,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-66,51; 8,85</t>
+          <t>-66,74; 17,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,4; 34,04</t>
+          <t>-55,47; 30,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 62,32</t>
+          <t>-22,37; 58,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,6; -25,17</t>
+          <t>-72,24; -26,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-82,1; -33,4</t>
+          <t>-83,43; -34,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 38,8</t>
+          <t>-25,08; 37,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-65,62; -27,22</t>
+          <t>-64,94; -27,99</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-68,92; -22,22</t>
+          <t>-66,52; -21,71</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,92</t>
+          <t>-3,74; 0,7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,95</t>
+          <t>-5,37; -1,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,19; -3,27</t>
+          <t>-7,18; -3,32</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,57</t>
+          <t>-1,42; 3,38</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 0,43</t>
+          <t>-3,69; 0,69</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -2,38</t>
+          <t>-5,99; -2,48</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,43</t>
+          <t>-1,92; 1,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -0,87</t>
+          <t>-3,87; -0,89</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -3,48</t>
+          <t>-6,11; -3,41</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 21,4</t>
+          <t>-53,09; 15,74</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-71,48; -14,24</t>
+          <t>-75,09; -22,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-96,43; -65,71</t>
+          <t>-96,27; -67,13</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 82,53</t>
+          <t>-20,76; 77,93</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 11,84</t>
+          <t>-54,39; 17,01</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-85,87; -51,74</t>
+          <t>-86,77; -54,22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 32,13</t>
+          <t>-29,49; 28,09</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-59,55; -16,24</t>
+          <t>-58,9; -17,13</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-90,45; -69,41</t>
+          <t>-90,77; -67,97</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,0</t>
+          <t>-1,14; 1,06</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,51</t>
+          <t>-1,57; 0,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -1,52</t>
+          <t>-3,59; -1,57</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,47</t>
+          <t>-0,96; 1,3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,34</t>
+          <t>-2,47; -0,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -2,45</t>
+          <t>-4,59; -2,45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,88</t>
+          <t>-0,72; 0,88</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,7; -0,2</t>
+          <t>-1,77; -0,24</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -2,27</t>
+          <t>-3,76; -2,31</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 23,47</t>
+          <t>-20,63; 24,66</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 11,96</t>
+          <t>-29,48; 14,64</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-66,75; -33,6</t>
+          <t>-67,27; -36,86</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 27,22</t>
+          <t>-14,14; 24,01</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -5,81</t>
+          <t>-38,07; -4,82</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-68,98; -44,91</t>
+          <t>-69,3; -45,29</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 17,79</t>
+          <t>-12,29; 17,9</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-29,5; -3,99</t>
+          <t>-30,23; -4,76</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-64,78; -45,72</t>
+          <t>-65,2; -45,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,71</t>
+          <t>-2,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-0,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 7,4</t>
+          <t>-0,44; 7,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 9,08</t>
+          <t>0,23; 9,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -1,66</t>
+          <t>-6,01; 0,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,78</t>
+          <t>0,79; 8,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,34</t>
+          <t>1,18; 9,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 6,24</t>
+          <t>-2,37; 5,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,07</t>
+          <t>1,28; 6,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,9</t>
+          <t>1,8; 7,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,41</t>
+          <t>-3,12; 1,93</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-93,2%</t>
+          <t>-62,81%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-42,57%</t>
+          <t>-19,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 310,73</t>
+          <t>-16,93; 312,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 407,34</t>
+          <t>-3,13; 396,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-98,44; -78,87</t>
+          <t>-89,58; 24,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 681,58</t>
+          <t>-2,05; 672,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 673,01</t>
+          <t>11,27; 683,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 561,16</t>
+          <t>-58,91; 365,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 319,09</t>
+          <t>21,99; 282,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,28; 385,99</t>
+          <t>30,67; 324,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,01; 117,26</t>
+          <t>-64,55; 90,53</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,97</t>
+          <t>-3,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,82</t>
+          <t>-2,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 4,72</t>
+          <t>-2,03; 4,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,28</t>
+          <t>-1,9; 4,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 3,43</t>
+          <t>-4,0; 2,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 0,47</t>
+          <t>-5,7; 0,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 2,06</t>
+          <t>-4,53; 1,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -2,35</t>
+          <t>-6,65; -0,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,72</t>
+          <t>-2,8; 1,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 2,3</t>
+          <t>-2,14; 2,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,0; -0,45</t>
+          <t>-4,26; 0,16</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-11,74%</t>
+          <t>-11,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-61,56%</t>
+          <t>-46,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-41,16%</t>
+          <t>-32,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 105,27</t>
+          <t>-29,05; 110,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 100,81</t>
+          <t>-27,89; 100,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 83,89</t>
+          <t>-57,01; 67,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 10,52</t>
+          <t>-57,38; 7,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 33,05</t>
+          <t>-47,97; 34,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,95; -33,65</t>
+          <t>-68,42; 0,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,81; 29,75</t>
+          <t>-35,69; 32,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 42,83</t>
+          <t>-27,68; 41,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-62,76; -3,3</t>
+          <t>-54,95; 3,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-2,66</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,77</t>
+          <t>-2,0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,86</t>
+          <t>-2,32</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; -0,61</t>
+          <t>-7,97; -0,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,24; -2,81</t>
+          <t>-9,75; -2,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 0,96</t>
+          <t>-7,18; 1,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,53</t>
+          <t>-6,02; 1,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,8</t>
+          <t>-6,4; 0,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 0,41</t>
+          <t>-5,62; 1,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -0,58</t>
+          <t>-5,85; -0,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -1,85</t>
+          <t>-6,55; -1,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,33</t>
+          <t>-5,09; 0,3</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-39,22%</t>
+          <t>-35,42%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,01%</t>
+          <t>-29,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-40,2%</t>
+          <t>-32,6%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,9; -6,02</t>
+          <t>-78,65; 1,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,57; -40,82</t>
+          <t>-93,59; -37,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,46; 21,75</t>
+          <t>-69,82; 26,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,6; 35,44</t>
+          <t>-67,4; 30,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 24,03</t>
+          <t>-69,25; 17,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 10,53</t>
+          <t>-64,29; 41,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,22; -9,08</t>
+          <t>-65,62; -5,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,29; -30,33</t>
+          <t>-75,7; -25,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,54; -3,26</t>
+          <t>-59,32; 5,55</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,48</t>
+          <t>-1,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,68</t>
+          <t>-0,95; 4,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,39</t>
+          <t>2,41; 9,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; -0,9</t>
+          <t>-4,02; 0,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,46</t>
+          <t>-2,96; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,84</t>
+          <t>-1,36; 5,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,82</t>
+          <t>-4,85; -0,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,96</t>
+          <t>-1,15; 2,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,11</t>
+          <t>1,28; 6,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,06; -1,23</t>
+          <t>-3,66; -0,4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-95,62%</t>
+          <t>-57,71%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-77,92%</t>
+          <t>-66,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-82,7%</t>
+          <t>-63,19%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 378,0</t>
+          <t>-38,51; 403,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45,52; 788,79</t>
+          <t>40,74; 802,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 231,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 110,17</t>
+          <t>-60,32; 106,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 210,92</t>
+          <t>-29,64; 235,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-95,04; -24,77</t>
+          <t>-90,53; 9,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 144,71</t>
+          <t>-26,78; 127,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,78; 268,9</t>
+          <t>27,73; 290,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-95,13; -52,67</t>
+          <t>-85,62; -12,39</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,32</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,78</t>
+          <t>-3,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 4,13</t>
+          <t>-3,8; 4,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,56</t>
+          <t>-4,59; 2,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; -1,41</t>
+          <t>-6,59; -1,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 5,1</t>
+          <t>-3,79; 5,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 1,57</t>
+          <t>-6,08; 1,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,37; -1,43</t>
+          <t>-8,55; -1,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,53</t>
+          <t>-2,33; 3,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,9</t>
+          <t>-4,18; 1,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -1,83</t>
+          <t>-6,38; -2,12</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-81,26%</t>
+          <t>-85,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-86,51%</t>
+          <t>-90,67%</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,78; 278,19</t>
+          <t>-68,76; 308,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,12; 194,95</t>
+          <t>-81,01; 216,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 163,3</t>
+          <t>-50,84; 199,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,39; 62,26</t>
+          <t>-76,54; 78,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-97,35; -13,78</t>
+          <t>-96,66; -46,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,65; 136,36</t>
+          <t>-37,6; 122,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 38,16</t>
+          <t>-66,93; 45,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-97,72; -31,9</t>
+          <t>-97,72; -68,32</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>0,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,41</t>
+          <t>-2,34; 2,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,18</t>
+          <t>-2,99; 1,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 2,27</t>
+          <t>-1,12; 4,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,55</t>
+          <t>-2,56; 3,46</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; -0,73</t>
+          <t>-5,03; -0,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,49</t>
+          <t>-3,48; 2,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,24</t>
+          <t>-1,43; 2,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,18; -0,15</t>
+          <t>-3,33; -0,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,26</t>
+          <t>-1,42; 2,48</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>100,28%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-31,82%</t>
+          <t>-14,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-14,71%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-87,3; 374,47</t>
+          <t>-84,45; 447,99</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 249,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-74,6; 355,54</t>
+          <t>-55,33; 704,37</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-54,13; 215,72</t>
+          <t>-54,69; 197,78</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,55</t>
+          <t>-100,0; 39,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,51; 101,27</t>
+          <t>-72,59; 123,48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 140,9</t>
+          <t>-42,69; 158,25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-90,3; 4,54</t>
+          <t>-90,74; 2,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 85,74</t>
+          <t>-41,92; 175,65</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-0,95</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-5,1</t>
+          <t>-3,52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-2,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,11</t>
+          <t>-2,9; 2,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,49</t>
+          <t>-4,24; 0,36</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,06</t>
+          <t>-3,27; 1,63</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,95</t>
+          <t>-2,46; 3,91</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -1,88</t>
+          <t>-7,49; -1,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -2,24</t>
+          <t>-6,38; -0,61</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,09</t>
+          <t>-1,97; 2,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,15; -1,68</t>
+          <t>-5,28; -1,54</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -1,25</t>
+          <t>-3,99; -0,3</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-23,01%</t>
+          <t>-18,61%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-59,85%</t>
+          <t>-41,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-46,88%</t>
+          <t>-32,89%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,85; 58,8</t>
+          <t>-45,96; 58,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 17,83</t>
+          <t>-67,02; 11,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,47; 30,45</t>
+          <t>-49,54; 46,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 58,7</t>
+          <t>-25,71; 60,86</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,24; -26,0</t>
+          <t>-71,95; -25,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-83,43; -34,59</t>
+          <t>-60,87; -8,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 37,48</t>
+          <t>-24,8; 41,43</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-64,94; -27,99</t>
+          <t>-65,94; -25,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-66,52; -21,71</t>
+          <t>-50,57; -4,66</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-5,07</t>
+          <t>-4,85</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-4,1</t>
+          <t>-3,57</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>-4,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,7</t>
+          <t>-3,83; 0,77</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,37; -1,1</t>
+          <t>-5,03; -0,94</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -3,32</t>
+          <t>-6,64; -2,97</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,38</t>
+          <t>-1,61; 3,33</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,69</t>
+          <t>-3,76; 0,7</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,99; -2,48</t>
+          <t>-5,59; -1,76</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,36</t>
+          <t>-1,84; 1,43</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -0,89</t>
+          <t>-3,82; -0,68</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -3,41</t>
+          <t>-5,75; -2,93</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-86,33%</t>
+          <t>-82,67%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-74,65%</t>
+          <t>-64,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-81,35%</t>
+          <t>-73,95%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-53,09; 15,74</t>
+          <t>-54,97; 16,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-75,09; -22,89</t>
+          <t>-72,69; -18,05</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-96,27; -67,13</t>
+          <t>-93,3; -58,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 77,93</t>
+          <t>-24,85; 73,46</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 17,01</t>
+          <t>-54,07; 18,02</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-86,77; -54,22</t>
+          <t>-79,98; -39,86</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 28,09</t>
+          <t>-28,79; 30,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-58,9; -17,13</t>
+          <t>-59,81; -13,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-90,77; -67,97</t>
+          <t>-84,72; -58,62</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-2,71</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-2,39</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,06</t>
+          <t>-1,11; 0,99</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,57</t>
+          <t>-1,55; 0,56</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -1,57</t>
+          <t>-3,08; -1,02</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,3</t>
+          <t>-1,01; 1,46</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,47; -0,27</t>
+          <t>-2,47; -0,37</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -2,45</t>
+          <t>-3,79; -1,62</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,88</t>
+          <t>-0,66; 0,87</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,24</t>
+          <t>-1,72; -0,18</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -2,31</t>
+          <t>-3,12; -1,68</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-52,91%</t>
+          <t>-42,89%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-58,53%</t>
+          <t>-45,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-56,03%</t>
+          <t>-44,22%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 24,66</t>
+          <t>-20,05; 24,23</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 14,64</t>
+          <t>-28,84; 13,14</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-67,27; -36,86</t>
+          <t>-57,29; -24,51</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 24,01</t>
+          <t>-15,36; 27,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-38,07; -4,82</t>
+          <t>-37,97; -7,14</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-69,3; -45,29</t>
+          <t>-56,91; -30,19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 17,9</t>
+          <t>-11,46; 17,32</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-30,23; -4,76</t>
+          <t>-29,75; -3,53</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-65,2; -45,67</t>
+          <t>-53,59; -33,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
